--- a/doc/DesignRationale.xlsx
+++ b/doc/DesignRationale.xlsx
@@ -4,14 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21855" windowHeight="11775" activeTab="3"/>
+    <workbookView windowWidth="21855" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="AM32固件可配置参数" sheetId="1" r:id="rId1"/>
     <sheet name="消隐功能" sheetId="2" r:id="rId2"/>
     <sheet name="电流采样" sheetId="3" r:id="rId3"/>
-    <sheet name="电流采样方式" sheetId="4" r:id="rId4"/>
-    <sheet name="知识说明" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="121">
   <si>
     <t>头部信息</t>
   </si>
@@ -1753,91 +1751,6 @@
   </si>
   <si>
     <t>其它MCU的方式待定</t>
-  </si>
-  <si>
-    <t>参考链接</t>
-  </si>
-  <si>
-    <t>【SimpleFOC】电流采样基础知识 - FBshark - 博客园</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>图例</t>
-  </si>
-  <si>
-    <t>低侧采样</t>
-  </si>
-  <si>
-    <t>可能是最常见的电流检测技术</t>
-  </si>
-  <si>
-    <t>不需要高性能的PWM抑制运放（如内置）</t>
-  </si>
-  <si>
-    <t>也不需要支持高压的运放（如高侧）</t>
-  </si>
-  <si>
-    <t>缺点：
-必须在下桥臂MOS打开时检测电流
-也就是：必须在电流流过采样电阻时去采样
-需要避开开关噪声，在MOS开关切换之后的稳定区去采样</t>
-  </si>
-  <si>
-    <t>PWM频率通常为20k～50khz
-这意味着低侧MOS的开关频率为每秒20k～50k次</t>
-  </si>
-  <si>
-    <t>最好是用那种支持硬件触发采样的MCU</t>
-  </si>
-  <si>
-    <t>将ADC设置成用timer触发，到达合适时机后进行采样</t>
-  </si>
-  <si>
-    <t>高侧采样</t>
-  </si>
-  <si>
-    <t>可能是最不常见的电流检测技术</t>
-  </si>
-  <si>
-    <t>需要运放支持高压：
-差分输入的两个电压是电源电压和高侧MOS的输入电压
-这两个电压都几乎等于电源电压，电压越高，运放耐压要求越高</t>
-  </si>
-  <si>
-    <t>因为共模电压高，所以需要高共模抑制比，降低共模泄露</t>
-  </si>
-  <si>
-    <t>缺点：
-和高侧采样一致，需要在下桥臂打开时采样</t>
-  </si>
-  <si>
-    <t>内置电流检测</t>
-  </si>
-  <si>
-    <t>是使用起来最简单但是最精准的技术</t>
-  </si>
-  <si>
-    <t>采样电阻串联在电机相线上，检测的电流始终都是电机相电流</t>
-  </si>
-  <si>
-    <t>因为电感中的电流不会突变
-所以无论PWM占空比的状态如何
-采样到的电流都是连续稳定的。</t>
-  </si>
-  <si>
-    <t>共模抑制比</t>
-  </si>
-  <si>
-    <t>以INA199A1DCKR为例，计算误差
-共模抑制比（CMRR）是100db
-同相输入端10V，反相输入端9.9V
-固定增益50</t>
-  </si>
-  <si>
-    <t>假设只知道电压、需要的误差等参数
-需要选型</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1773,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1868,7 +1781,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2493,26 +2406,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2828,352 +2732,6 @@
         <a:xfrm>
           <a:off x="1400175" y="590550"/>
           <a:ext cx="2600325" cy="1228725"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>74295</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>511810</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="image"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9475470" y="5467350"/>
-          <a:ext cx="7200265" cy="4584700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>32385</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>146685</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>141605</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3" descr="image"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9433560" y="11138535"/>
-          <a:ext cx="7200265" cy="3423920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>85090</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>522605</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4" descr="image"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9486265" y="581025"/>
-          <a:ext cx="7200265" cy="4225925"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4219575" y="47625"/>
-          <a:ext cx="4524375" cy="6534150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8810625" y="123825"/>
-          <a:ext cx="4067175" cy="1095375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4343400" y="7096125"/>
-          <a:ext cx="3305175" cy="3505200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8591550" y="7343775"/>
-          <a:ext cx="5629275" cy="8105775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1571625</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="图片 6"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3228975" y="10772775"/>
-          <a:ext cx="5029200" cy="2009775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3442,31 +3000,31 @@
   <dimension ref="B1:D48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="26" style="4" customWidth="1"/>
+    <col min="2" max="2" width="26" style="1" customWidth="1"/>
     <col min="3" max="3" width="53.75" customWidth="1"/>
     <col min="4" max="4" width="60.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" spans="2:4">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" ht="14.25" spans="2:4">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="2:4">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
@@ -3474,7 +3032,7 @@
       </c>
     </row>
     <row r="4" ht="14.25" spans="2:4">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
@@ -3482,7 +3040,7 @@
       </c>
     </row>
     <row r="5" ht="14.25" spans="2:4">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
@@ -3490,7 +3048,7 @@
       </c>
     </row>
     <row r="6" ht="14.25" spans="2:4">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
@@ -3498,25 +3056,25 @@
       </c>
     </row>
     <row r="9" ht="18.75" spans="2:4">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" ht="14.25" spans="2:4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="2:4">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
@@ -3527,7 +3085,7 @@
       </c>
     </row>
     <row r="12" ht="14.25" spans="2:4">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
@@ -3538,7 +3096,7 @@
       </c>
     </row>
     <row r="13" ht="14.25" spans="2:4">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C13" t="s">
@@ -3546,153 +3104,153 @@
       </c>
     </row>
     <row r="14" ht="40.5" spans="2:4">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" ht="54" spans="2:4">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" ht="67.5" spans="2:4">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="81" spans="2:4">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" ht="27" spans="2:4">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" ht="54" spans="2:4">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" ht="67.5" spans="2:4">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" ht="94.5" spans="2:4">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C21" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" ht="18.75" spans="2:4">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" ht="14.25" spans="2:4">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="2:4">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C26" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="2:4">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" ht="18.75" spans="2:4">
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" ht="14.25" spans="2:4">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" ht="14.25" spans="2:4">
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C32" t="s">
@@ -3700,7 +3258,7 @@
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:4">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C33" t="s">
@@ -3708,7 +3266,7 @@
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C34" t="s">
@@ -3716,7 +3274,7 @@
       </c>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C35" t="s">
@@ -3724,7 +3282,7 @@
       </c>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C36" t="s">
@@ -3732,7 +3290,7 @@
       </c>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C37" t="s">
@@ -3740,7 +3298,7 @@
       </c>
     </row>
     <row r="38" ht="14.25" spans="2:4">
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C38" t="s">
@@ -3748,7 +3306,7 @@
       </c>
     </row>
     <row r="39" ht="14.25" spans="2:4">
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C39" t="s">
@@ -3756,7 +3314,7 @@
       </c>
     </row>
     <row r="40" ht="14.25" spans="2:4">
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C40" t="s">
@@ -3764,7 +3322,7 @@
       </c>
     </row>
     <row r="41" ht="14.25" spans="2:4">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C41" t="s">
@@ -3772,7 +3330,7 @@
       </c>
     </row>
     <row r="42" ht="14.25" spans="2:4">
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C42" t="s">
@@ -3780,7 +3338,7 @@
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C43" t="s">
@@ -3788,7 +3346,7 @@
       </c>
     </row>
     <row r="44" ht="14.25" spans="2:4">
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C44" t="s">
@@ -3796,7 +3354,7 @@
       </c>
     </row>
     <row r="45" ht="14.25" spans="2:4">
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C45" t="s">
@@ -3804,7 +3362,7 @@
       </c>
     </row>
     <row r="46" ht="14.25" spans="2:4">
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C46" t="s">
@@ -3812,7 +3370,7 @@
       </c>
     </row>
     <row r="47" spans="2:4">
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C47" t="s">
@@ -3820,13 +3378,13 @@
       </c>
     </row>
     <row r="48" ht="81" spans="2:4">
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="4" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4015,431 +3573,4 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:E64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
-  <cols>
-    <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="63.5" customWidth="1"/>
-    <col min="4" max="4" width="37.375" customWidth="1"/>
-    <col min="5" max="5" width="34.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:5">
-      <c r="B1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" ht="14.25" spans="2:5">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:5">
-      <c r="B3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="C5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="C6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" ht="54" spans="2:5">
-      <c r="C8" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="2:5">
-      <c r="C9" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="C11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="C12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="B28" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" ht="40.5" spans="2:3">
-      <c r="C29" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3">
-      <c r="C31" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" ht="27" spans="3:3">
-      <c r="C33" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3">
-      <c r="B58" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C58" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3">
-      <c r="C59" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="60" ht="40.5" spans="2:3">
-      <c r="C60" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3">
-      <c r="C64" s="2"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C1" r:id="rId2" display="【SimpleFOC】电流采样基础知识 - FBshark - 博客园" tooltip="https://www.cnblogs.com/FBsharl/p/19115974"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B3:C85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
-  <cols>
-    <col min="2" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="32.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" ht="54" spans="2:3">
-      <c r="B3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="2:3">
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="2:3">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="2:3">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="2:3">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="2:3">
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="2:3">
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="2:3">
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="2:3">
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="2:3">
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="2:3">
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" ht="27" spans="2:3">
-      <c r="B40" s="1"/>
-      <c r="C40" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3">
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="2:3">
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="2:3">
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="2:3">
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="2:3">
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="2:3">
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="2:3">
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="2:3">
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="1"/>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" s="1"/>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="1"/>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="1"/>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="1"/>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="1"/>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="1"/>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="1"/>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="1"/>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="1"/>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="1"/>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="1"/>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" s="1"/>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" s="1"/>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" s="1"/>
-    </row>
-    <row r="68" spans="2:2">
-      <c r="B68" s="1"/>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="1"/>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="1"/>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71" s="1"/>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="1"/>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="1"/>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="1"/>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76" s="1"/>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" s="1"/>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" s="1"/>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="1"/>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="1"/>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="1"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="1"/>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="1"/>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:B85"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>